--- a/public/templates/import-product-variants.xlsx
+++ b/public/templates/import-product-variants.xlsx
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -660,39 +660,53 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="6" customHeight="1">
-      <c r="A18" s="2" t="inlineStr"/>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * standard_code       -&gt; Codigo UNSPSC/EAN del producto para el XML FE (opcional).</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * standard_code_type  -&gt; Tipo de codigo: UNSPSC | EAN | GTIN | PARTNUM (default UNSPSC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="6" customHeight="1">
+      <c r="A20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>NOTAS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * No modifiques los nombres de las columnas (fila 1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * No elimines las hojas productos, unidades_dian o listas_ref.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Las filas en blanco se ignoran.</t>
+          <t xml:space="preserve">  * No modifiques los nombres de las columnas (fila 1).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * No elimines las hojas productos, unidades_dian o listas_ref.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Las filas en blanco se ignoran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  * Booleanos aceptan: TRUE / FALSE (en mayusculas).</t>
         </is>
@@ -709,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -727,6 +741,8 @@
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -805,6 +821,16 @@
           <t>location_code</t>
         </is>
       </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>standard_code</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>standard_code_type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
@@ -872,9 +898,15 @@
           <t>PRINCIPAL</t>
         </is>
       </c>
+      <c r="P2" s="8" t="inlineStr"/>
+      <c r="Q2" s="8" t="inlineStr">
+        <is>
+          <t>UNSPSC</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="8">
     <dataValidation sqref="C2:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Selecciona de la lista (unidades_dian)" type="list">
       <formula1>=unidades_dian!$A$2:$A$42</formula1>
     </dataValidation>
@@ -896,6 +928,9 @@
     <dataValidation sqref="N2:N1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Selecciona de la lista (listas_ref)" type="list">
       <formula1>=listas_ref!$G$2:$G$3</formula1>
     </dataValidation>
+    <dataValidation sqref="Q2:Q1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Selecciona de la lista (listas_ref)" type="list">
+      <formula1>=listas_ref!$I$2:$I$5</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1845,7 +1880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1881,6 +1916,16 @@
           <t>booleanos</t>
         </is>
       </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>standard_code_type</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1908,6 +1953,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>UNSPSC</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Codigo global de producto/servicio</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1935,6 +1990,16 @@
           <t>FALSE</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>EAN</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Codigo de barras EAN-13</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1957,6 +2022,16 @@
           <t>Producto fabricado</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>GTIN</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Numero global de articulo comercial</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="D5" t="inlineStr">
@@ -1967,6 +2042,16 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>Paquete/combo</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PARTNUM</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Numero de parte fabricante</t>
         </is>
       </c>
     </row>
